--- a/example/GRAFS_data_example_C_prospect.xlsx
+++ b/example/GRAFS_data_example_C_prospect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F03168-A32D-4F40-AACD-8FEEB55A0239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DE6695-457C-4943-B968-640287EF76B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F475FEA0-B9E5-4A03-9EDE-4A3E6C5C262C}"/>
+    <workbookView xWindow="16530" yWindow="-15870" windowWidth="25440" windowHeight="15270" xr2:uid="{F475FEA0-B9E5-4A03-9EDE-4A3E6C5C262C}"/>
   </bookViews>
   <sheets>
     <sheet name="Input data" sheetId="2" r:id="rId1"/>

--- a/example/GRAFS_data_example_C_prospect.xlsx
+++ b/example/GRAFS_data_example_C_prospect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DE6695-457C-4943-B968-640287EF76B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A475F1-12D7-4924-BC7F-8E74CEE21757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16530" yWindow="-15870" windowWidth="25440" windowHeight="15270" xr2:uid="{F475FEA0-B9E5-4A03-9EDE-4A3E6C5C262C}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="89">
   <si>
     <t>Area</t>
   </si>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D825A9-0C1C-44E4-98B7-F194F26ABDB6}">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" customWidth="1"/>
@@ -2994,7 +2994,7 @@
         <v>5</v>
       </c>
       <c r="B126">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>35</v>
@@ -3003,7 +3003,7 @@
         <v>41</v>
       </c>
       <c r="E126">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
@@ -3011,16 +3011,16 @@
         <v>5</v>
       </c>
       <c r="B127">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E127">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
@@ -3028,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="B128">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>35</v>
@@ -3037,7 +3037,7 @@
         <v>42</v>
       </c>
       <c r="E128">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
@@ -3045,16 +3045,16 @@
         <v>5</v>
       </c>
       <c r="B129">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E129">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
@@ -3062,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="B130">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>35</v>
@@ -3085,10 +3085,10 @@
         <v>35</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E131">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
@@ -3102,10 +3102,10 @@
         <v>35</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
@@ -3119,10 +3119,10 @@
         <v>35</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E133">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
@@ -3130,16 +3130,16 @@
         <v>5</v>
       </c>
       <c r="B134">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E134">
-        <v>0.05</v>
+        <v>61</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="B135">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>35</v>
@@ -3156,7 +3156,7 @@
         <v>61</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
@@ -3167,13 +3167,13 @@
         <v>2023</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
+      </c>
+      <c r="D136" t="s">
+        <v>14</v>
+      </c>
+      <c r="E136" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
@@ -3187,10 +3187,10 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
@@ -3204,10 +3204,10 @@
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E138" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
@@ -3215,16 +3215,16 @@
         <v>5</v>
       </c>
       <c r="B139">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
@@ -3238,10 +3238,10 @@
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
@@ -3255,27 +3255,27 @@
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E141" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>5</v>
       </c>
       <c r="B142">
         <v>1961</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" t="s">
         <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E142" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
@@ -3283,7 +3283,7 @@
         <v>5</v>
       </c>
       <c r="B143">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C143" t="s">
         <v>25</v>
@@ -3296,155 +3296,155 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>5</v>
-      </c>
-      <c r="B144">
-        <v>2023</v>
-      </c>
-      <c r="C144" t="s">
-        <v>25</v>
-      </c>
-      <c r="D144" t="s">
-        <v>80</v>
-      </c>
-      <c r="E144" t="s">
-        <v>76</v>
+      <c r="A144" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B144" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E144" s="8">
+        <v>2.76</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A145" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B145" s="2">
-        <v>1961</v>
-      </c>
-      <c r="C145" s="5" t="s">
+      <c r="A145" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>59</v>
+      <c r="D145" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="E145" s="8">
-        <v>2.76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A146" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B146" s="3">
-        <v>1961</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>52</v>
+      <c r="A146" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="E146" s="8">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B147" s="2">
+      <c r="A147" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" s="3">
         <v>1961</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>6</v>
+      <c r="D147" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E147" s="8">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A148" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B148" s="3">
+      <c r="A148" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" s="2">
         <v>1961</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D148" s="6" t="s">
-        <v>58</v>
+      <c r="D148" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E148" s="8">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B149" s="2">
+      <c r="A149" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" s="3">
         <v>1961</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D149" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E149" s="8">
-        <v>2.2000000000000002</v>
+      <c r="D149" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B150" s="3">
+      <c r="A150" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" s="2">
         <v>1961</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D150" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E150" s="4">
-        <v>0</v>
+      <c r="D150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="8">
+        <v>3.5</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B151" s="2">
+      <c r="A151" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" s="3">
         <v>1961</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="8">
-        <v>3.5</v>
+      <c r="D151" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A152" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B152" s="3">
+      <c r="A152" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152" s="2">
         <v>1961</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="11">
+      <c r="D152" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E152" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3453,117 +3453,117 @@
         <v>5</v>
       </c>
       <c r="B153" s="2">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E153" s="12">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="E153" s="8">
+        <v>2.5</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B154" s="2">
+      <c r="A154" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B154" s="3">
         <v>2023</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>6</v>
+      <c r="D154" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E154" s="8">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B155" s="3">
+      <c r="A155" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155" s="2">
         <v>2023</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D155" s="6" t="s">
-        <v>58</v>
+      <c r="D155" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E155" s="8">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A156" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B156" s="2">
+      <c r="A156" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156" s="3">
         <v>2023</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E156" s="8">
-        <v>2.2000000000000002</v>
+      <c r="D156" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B157" s="3">
+      <c r="A157" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" s="2">
         <v>2023</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D157" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E157" s="4">
-        <v>0</v>
+      <c r="D157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="8">
+        <v>3.5</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B158" s="2">
+      <c r="A158" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158" s="3">
         <v>2023</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="8">
-        <v>3.5</v>
+      <c r="D158" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B159" s="3">
+      <c r="A159" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159" s="2">
         <v>2023</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D159" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="11">
+      <c r="D159" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3572,118 +3572,118 @@
         <v>5</v>
       </c>
       <c r="B160" s="2">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E160" s="12">
+        <v>6</v>
+      </c>
+      <c r="E160">
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A161" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B161" s="2">
+      <c r="A161" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161" s="3">
         <v>1961</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>6</v>
+      <c r="D161" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B162" s="3">
+      <c r="A162" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162" s="2">
         <v>1961</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D162" s="6" t="s">
-        <v>58</v>
+      <c r="D162" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B163" s="2">
+      <c r="A163" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="3">
         <v>1961</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>7</v>
+      <c r="D163" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B164" s="3">
+      <c r="A164" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" s="2">
         <v>1961</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D164" s="6" t="s">
-        <v>8</v>
+      <c r="D164" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E164">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B165" s="2">
+      <c r="A165" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165" s="3">
         <v>1961</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>9</v>
+      <c r="D165" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A166" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B166" s="3">
+      <c r="A166" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" s="2">
         <v>1961</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D166" s="6" t="s">
-        <v>11</v>
+      <c r="D166" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
@@ -3691,135 +3691,135 @@
         <v>5</v>
       </c>
       <c r="B167" s="2">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E167">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A168" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B168" s="2">
+      <c r="A168" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B168" s="3">
         <v>2023</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>6</v>
+      <c r="D168" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B169" s="3">
+      <c r="A169" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B169" s="2">
         <v>2023</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D169" s="6" t="s">
-        <v>58</v>
+      <c r="D169" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A170" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B170" s="2">
+      <c r="A170" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B170" s="3">
         <v>2023</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>7</v>
+      <c r="D170" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A171" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B171" s="3">
+      <c r="A171" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B171" s="2">
         <v>2023</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D171" s="6" t="s">
-        <v>8</v>
+      <c r="D171" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E171">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A172" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B172" s="2">
+      <c r="A172" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B172" s="3">
         <v>2023</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>9</v>
+      <c r="D172" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A173" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B173" s="3">
+      <c r="A173" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B173" s="2">
         <v>2023</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D173" s="6" t="s">
-        <v>11</v>
+      <c r="D173" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A174" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B174" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>22</v>
+      <c r="A174" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" s="14">
+        <v>1961</v>
+      </c>
+      <c r="C174" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" t="s">
+        <v>39</v>
       </c>
       <c r="E174">
-        <v>150</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="B175" s="14">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C175" s="15" t="s">
         <v>12</v>
@@ -3836,23 +3836,6 @@
         <v>39</v>
       </c>
       <c r="E175">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A176" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B176" s="14">
-        <v>2023</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D176" t="s">
-        <v>39</v>
-      </c>
-      <c r="E176">
         <v>25</v>
       </c>
     </row>

--- a/example/GRAFS_data_example_C_prospect.xlsx
+++ b/example/GRAFS_data_example_C_prospect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faustega\Documents\These\isterre-dynamic-modeling\grafs-e-project\grafs-e\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A475F1-12D7-4924-BC7F-8E74CEE21757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC44F433-6044-4E0A-BAB2-88ED4B9E2FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16530" yWindow="-15870" windowWidth="25440" windowHeight="15270" xr2:uid="{F475FEA0-B9E5-4A03-9EDE-4A3E6C5C262C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F475FEA0-B9E5-4A03-9EDE-4A3E6C5C262C}"/>
   </bookViews>
   <sheets>
     <sheet name="Input data" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Energy power" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">'Input data'!$A$1:$E$97</definedName>
+    <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">'Input data'!$A$1:$E$153</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="86">
   <si>
     <t>Area</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Soya beans</t>
   </si>
   <si>
-    <t>Production (kton)</t>
-  </si>
-  <si>
     <t>Area (ha)</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>fr_1961_fr</t>
   </si>
   <si>
-    <t>Non edible porcines carcass</t>
-  </si>
-  <si>
     <t>Atmospheric deposition coef (kgN/ha)</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
   </si>
   <si>
     <t>Soya beans grain</t>
-  </si>
-  <si>
-    <t>Natural meadow forage</t>
   </si>
   <si>
     <t>Maize</t>
@@ -464,10 +455,7 @@
   <dxfs count="4">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -476,9 +464,10 @@
         <bottom style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -524,14 +513,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C19122AA-E7CC-4368-B59D-7B0737AF5C9D}" name="production_france" displayName="production_france" ref="A1:E97" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E97" xr:uid="{C19122AA-E7CC-4368-B59D-7B0737AF5C9D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C19122AA-E7CC-4368-B59D-7B0737AF5C9D}" name="production_france" displayName="production_france" ref="A1:E153" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E153" xr:uid="{C19122AA-E7CC-4368-B59D-7B0737AF5C9D}"/>
   <tableColumns count="5">
-    <tableColumn id="3" xr3:uid="{7B352F64-988D-49A0-B664-7D1BD688EE1B}" uniqueName="3" name="Area" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{7B352F64-988D-49A0-B664-7D1BD688EE1B}" uniqueName="3" name="Area" queryTableFieldId="3" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{E88EBC76-2C3C-4BE6-B345-902903CB70D2}" uniqueName="4" name="Year" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{C56568E9-7386-48BB-AE51-0A3400CB0D14}" uniqueName="5" name="category" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{583513EB-334C-4C54-BF53-D669A066B6B7}" uniqueName="10" name="item" queryTableFieldId="10" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{91174CF9-2FC0-4CE8-B60F-7E15C76A8221}" uniqueName="11" name="value" queryTableFieldId="11" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{C56568E9-7386-48BB-AE51-0A3400CB0D14}" uniqueName="5" name="category" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{583513EB-334C-4C54-BF53-D669A066B6B7}" uniqueName="10" name="item" queryTableFieldId="10" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{91174CF9-2FC0-4CE8-B60F-7E15C76A8221}" uniqueName="11" name="value" queryTableFieldId="11" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -854,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D825A9-0C1C-44E4-98B7-F194F26ABDB6}">
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E333"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" customWidth="1"/>
@@ -892,10 +881,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>15000</v>
+        <v>2259100</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -909,10 +898,10 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E3">
-        <v>7500</v>
+        <v>980600</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -926,10 +915,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>2590.69</v>
+        <v>1441170</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -943,10 +932,10 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>133.69</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -960,10 +949,10 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>25000</v>
+        <v>3997300</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -977,10 +966,10 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>600</v>
+        <v>257750</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -994,10 +983,10 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>10000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1005,16 +994,16 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>1448</v>
+        <v>1815490</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1022,16 +1011,16 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E10">
-        <v>1188</v>
+        <v>1314680</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1039,16 +1028,16 @@
         <v>5</v>
       </c>
       <c r="B11">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>19069.295999999998</v>
+        <v>78900</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1062,10 +1051,10 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>12143.49</v>
+        <v>12120</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1079,10 +1068,10 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>12834.6</v>
+        <v>4998280</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1096,10 +1085,10 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>337.34</v>
+        <v>157750</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1113,10 +1102,10 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>68.27</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1124,16 +1113,16 @@
         <v>5</v>
       </c>
       <c r="B16">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>35995.57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1141,16 +1130,16 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E17">
-        <v>387.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1158,16 +1147,16 @@
         <v>5</v>
       </c>
       <c r="B18">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E18">
-        <v>5000</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1175,16 +1164,16 @@
         <v>5</v>
       </c>
       <c r="B19">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E19">
-        <v>1301.42</v>
+        <v>19501008</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1192,16 +1181,16 @@
         <v>5</v>
       </c>
       <c r="B20">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20">
-        <v>2062.46</v>
+        <v>46.800000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1209,16 +1198,16 @@
         <v>5</v>
       </c>
       <c r="B21">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21">
         <v>10</v>
-      </c>
-      <c r="E21">
-        <v>23882</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1229,13 +1218,13 @@
         <v>1961</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="E22">
-        <v>2259100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1246,13 +1235,13 @@
         <v>1961</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E23">
-        <v>980600</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1263,13 +1252,13 @@
         <v>1961</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E24">
-        <v>1441170</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1280,13 +1269,13 @@
         <v>1961</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E25">
-        <v>33000</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1297,13 +1286,13 @@
         <v>1961</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E26">
-        <v>3997300</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1314,13 +1303,13 @@
         <v>1961</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="E27">
-        <v>257750</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1331,13 +1320,13 @@
         <v>1961</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>10000000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -1345,16 +1334,16 @@
         <v>5</v>
       </c>
       <c r="B29">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>1815490</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1362,16 +1351,16 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>1314680</v>
+        <v>8603000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1379,16 +1368,16 @@
         <v>5</v>
       </c>
       <c r="B31">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E31">
-        <v>78900</v>
+        <v>35.880000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -1396,16 +1385,16 @@
         <v>5</v>
       </c>
       <c r="B32">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E32">
-        <v>12120</v>
+        <v>46.800000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1413,16 +1402,16 @@
         <v>5</v>
       </c>
       <c r="B33">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="E33">
-        <v>4998280</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1430,16 +1419,16 @@
         <v>5</v>
       </c>
       <c r="B34">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E34">
-        <v>157750</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1447,16 +1436,16 @@
         <v>5</v>
       </c>
       <c r="B35">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E35">
-        <v>3000000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1467,13 +1456,13 @@
         <v>1961</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E36">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1484,13 +1473,13 @@
         <v>1961</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E37">
-        <v>80</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1501,13 +1490,13 @@
         <v>1961</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="E38">
-        <v>150</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1518,13 +1507,13 @@
         <v>1961</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>19501008</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1532,16 +1521,16 @@
         <v>5</v>
       </c>
       <c r="B40">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>46.800000000000004</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1549,16 +1538,16 @@
         <v>5</v>
       </c>
       <c r="B41">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -1566,16 +1555,16 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E42">
-        <v>40</v>
+        <v>19501008</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1583,16 +1572,16 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>35.880000000000003</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1600,16 +1589,16 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>46.800000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -1617,16 +1606,16 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E45">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -1634,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E46">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1651,16 +1640,16 @@
         <v>5</v>
       </c>
       <c r="B47">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -1668,13 +1657,13 @@
         <v>5</v>
       </c>
       <c r="B48">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E48">
         <v>10</v>
@@ -1685,16 +1674,16 @@
         <v>5</v>
       </c>
       <c r="B49">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E49">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -1702,16 +1691,16 @@
         <v>5</v>
       </c>
       <c r="B50">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E50">
-        <v>8603000</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -1719,16 +1708,16 @@
         <v>5</v>
       </c>
       <c r="B51">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E51">
-        <v>35.880000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -1736,16 +1725,16 @@
         <v>5</v>
       </c>
       <c r="B52">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="E52">
-        <v>46.800000000000004</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -1753,16 +1742,16 @@
         <v>5</v>
       </c>
       <c r="B53">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E53">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -1770,16 +1759,16 @@
         <v>5</v>
       </c>
       <c r="B54">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E54">
-        <v>35</v>
+        <v>8603000</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -1787,16 +1776,16 @@
         <v>5</v>
       </c>
       <c r="B55">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C55" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>35.880000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -1804,16 +1793,16 @@
         <v>5</v>
       </c>
       <c r="B56">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E56">
-        <v>30</v>
+        <v>46.800000000000004</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -1821,16 +1810,16 @@
         <v>5</v>
       </c>
       <c r="B57">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -1838,16 +1827,16 @@
         <v>5</v>
       </c>
       <c r="B58">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E58">
-        <v>0.2</v>
+        <v>28.999999999999996</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -1855,16 +1844,16 @@
         <v>5</v>
       </c>
       <c r="B59">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
         <v>70</v>
       </c>
-      <c r="D59" t="s">
-        <v>74</v>
-      </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -1875,13 +1864,13 @@
         <v>2023</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E60">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -1892,13 +1881,13 @@
         <v>2023</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="E61">
-        <v>150</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -1909,13 +1898,13 @@
         <v>2023</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="E62">
-        <v>19501008</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -1926,13 +1915,13 @@
         <v>2023</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E63">
-        <v>35.880000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -1940,16 +1929,16 @@
         <v>5</v>
       </c>
       <c r="B64">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
-      </c>
-      <c r="D64" t="s">
-        <v>67</v>
+        <v>17</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E64">
-        <v>46.800000000000004</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -1957,16 +1946,16 @@
         <v>5</v>
       </c>
       <c r="B65">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
-      </c>
-      <c r="D65" t="s">
-        <v>68</v>
+        <v>46</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>11.799999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -1974,16 +1963,16 @@
         <v>5</v>
       </c>
       <c r="B66">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" t="s">
-        <v>69</v>
+        <v>47</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E66">
-        <v>2.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -1991,16 +1980,16 @@
         <v>5</v>
       </c>
       <c r="B67">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" t="s">
-        <v>67</v>
+        <v>48</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E67">
-        <v>1.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2008,16 +1997,16 @@
         <v>5</v>
       </c>
       <c r="B68">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C68" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" t="s">
-        <v>68</v>
+        <v>18</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E68">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -2025,16 +2014,16 @@
         <v>5</v>
       </c>
       <c r="B69">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C69" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" t="s">
-        <v>69</v>
+        <v>78</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E69">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -2042,16 +2031,16 @@
         <v>5</v>
       </c>
       <c r="B70">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C70" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E70">
-        <v>0.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -2062,13 +2051,13 @@
         <v>2023</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" t="s">
-        <v>68</v>
+        <v>17</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>70000000</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -2079,13 +2068,13 @@
         <v>2023</v>
       </c>
       <c r="C72" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" t="s">
-        <v>15</v>
+        <v>46</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E72">
-        <v>20</v>
+        <v>11.799999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -2096,13 +2085,13 @@
         <v>2023</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E73">
-        <v>100</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -2113,13 +2102,13 @@
         <v>2023</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E74">
-        <v>8603000</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -2130,13 +2119,13 @@
         <v>2023</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
-      </c>
-      <c r="D75" t="s">
-        <v>72</v>
+        <v>18</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="E75">
-        <v>35.880000000000003</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -2147,13 +2136,13 @@
         <v>2023</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E76">
-        <v>46.800000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -2164,353 +2153,353 @@
         <v>2023</v>
       </c>
       <c r="C77" t="s">
-        <v>66</v>
-      </c>
-      <c r="D77" t="s">
-        <v>74</v>
+        <v>19</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>20</v>
       </c>
       <c r="E77">
         <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B78">
-        <v>2023</v>
-      </c>
-      <c r="C78" t="s">
-        <v>71</v>
-      </c>
-      <c r="D78" t="s">
-        <v>72</v>
-      </c>
-      <c r="E78">
-        <v>28.999999999999996</v>
+        <v>1961</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E78" s="1">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B79">
-        <v>2023</v>
-      </c>
-      <c r="C79" t="s">
-        <v>71</v>
-      </c>
-      <c r="D79" t="s">
-        <v>73</v>
-      </c>
-      <c r="E79">
-        <v>1</v>
+        <v>1961</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E79" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B80">
-        <v>2023</v>
-      </c>
-      <c r="C80" t="s">
-        <v>71</v>
-      </c>
-      <c r="D80" t="s">
-        <v>74</v>
-      </c>
-      <c r="E80">
-        <v>10</v>
+        <v>1961</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B81">
-        <v>2023</v>
-      </c>
-      <c r="C81" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" t="s">
-        <v>72</v>
-      </c>
-      <c r="E81">
-        <v>4</v>
+        <v>1961</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B82">
-        <v>2023</v>
-      </c>
-      <c r="C82" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" t="s">
-        <v>73</v>
-      </c>
-      <c r="E82">
-        <v>0.2</v>
+        <v>1961</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="1">
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B83">
-        <v>2023</v>
-      </c>
-      <c r="C83" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" t="s">
-        <v>74</v>
+        <v>1961</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B84">
         <v>1961</v>
       </c>
-      <c r="C84" t="s">
-        <v>18</v>
-      </c>
-      <c r="D84" s="16" t="s">
+      <c r="C84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E84">
-        <v>40000000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B85">
-        <v>1961</v>
-      </c>
-      <c r="C85" t="s">
-        <v>48</v>
-      </c>
-      <c r="D85" s="17" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86">
+        <v>2023</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E86" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87">
+        <v>2023</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88">
+        <v>2023</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89">
+        <v>2023</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90">
+        <v>2023</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91">
+        <v>2023</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E85">
-        <v>11.799999999999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>5</v>
-      </c>
-      <c r="B86">
-        <v>1961</v>
-      </c>
-      <c r="C86" t="s">
-        <v>49</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E86">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>5</v>
-      </c>
-      <c r="B87">
-        <v>1961</v>
-      </c>
-      <c r="C87" t="s">
-        <v>50</v>
-      </c>
-      <c r="D87" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E87">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>5</v>
-      </c>
-      <c r="B88">
-        <v>1961</v>
-      </c>
-      <c r="C88" t="s">
-        <v>19</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E88">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>5</v>
-      </c>
-      <c r="B89">
-        <v>1961</v>
-      </c>
-      <c r="C89" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>5</v>
-      </c>
-      <c r="B90">
-        <v>1961</v>
-      </c>
-      <c r="C90" t="s">
-        <v>20</v>
-      </c>
-      <c r="D90" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91">
-        <v>2023</v>
-      </c>
-      <c r="C91" t="s">
-        <v>18</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>21</v>
-      </c>
       <c r="E91">
-        <v>70000000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B92">
-        <v>2023</v>
-      </c>
-      <c r="C92" t="s">
-        <v>48</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E92">
-        <v>11.799999999999999</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B93">
-        <v>2023</v>
-      </c>
-      <c r="C93" t="s">
-        <v>49</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E93">
-        <v>42.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B94">
-        <v>2023</v>
-      </c>
-      <c r="C94" t="s">
-        <v>50</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E94">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B95">
-        <v>2023</v>
-      </c>
-      <c r="C95" t="s">
-        <v>19</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B96">
-        <v>2023</v>
-      </c>
-      <c r="C96" t="s">
-        <v>81</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="E96">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B97">
-        <v>2023</v>
-      </c>
-      <c r="C97" t="s">
-        <v>20</v>
-      </c>
-      <c r="D97" s="17" t="s">
-        <v>21</v>
+        <v>1961</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -2524,10 +2513,10 @@
         <v>23</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E98" s="1">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -2535,16 +2524,16 @@
         <v>5</v>
       </c>
       <c r="B99">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E99" s="1">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="E99">
+        <v>0.03</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -2552,16 +2541,16 @@
         <v>5</v>
       </c>
       <c r="B100">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" s="1">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="E100">
+        <v>0.03</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -2569,16 +2558,16 @@
         <v>5</v>
       </c>
       <c r="B101">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="1">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E101">
+        <v>0.03</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -2586,16 +2575,16 @@
         <v>5</v>
       </c>
       <c r="B102">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="1">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="E102">
+        <v>0.03</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
@@ -2603,16 +2592,16 @@
         <v>5</v>
       </c>
       <c r="B103">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -2620,16 +2609,16 @@
         <v>5</v>
       </c>
       <c r="B104">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E104">
-        <v>25</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -2643,10 +2632,10 @@
         <v>23</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E105" s="1">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
@@ -2657,13 +2646,13 @@
         <v>2023</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E106" s="1">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="E106">
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
@@ -2671,16 +2660,16 @@
         <v>5</v>
       </c>
       <c r="B107">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E107" s="1">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="E107">
+        <v>50</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -2691,13 +2680,13 @@
         <v>2023</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E108" s="1">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="E108">
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -2705,16 +2694,16 @@
         <v>5</v>
       </c>
       <c r="B109">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="1">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="E109">
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -2725,13 +2714,13 @@
         <v>2023</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -2742,13 +2731,13 @@
         <v>2023</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E111">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
@@ -2756,16 +2745,16 @@
         <v>5</v>
       </c>
       <c r="B112">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E112">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
@@ -2773,16 +2762,16 @@
         <v>5</v>
       </c>
       <c r="B113">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E113">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -2793,13 +2782,13 @@
         <v>1961</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E114">
-        <v>0.03</v>
+        <v>58</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
@@ -2807,16 +2796,16 @@
         <v>5</v>
       </c>
       <c r="B115">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115">
-        <v>0.03</v>
+        <v>58</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -2824,16 +2813,16 @@
         <v>5</v>
       </c>
       <c r="B116">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116">
-        <v>0.03</v>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -2841,16 +2830,16 @@
         <v>5</v>
       </c>
       <c r="B117">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117">
-        <v>0.03</v>
+      <c r="D117" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
@@ -2858,16 +2847,16 @@
         <v>5</v>
       </c>
       <c r="B118">
-        <v>1961</v>
+        <v>2023</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
+      <c r="D118" t="s">
+        <v>20</v>
+      </c>
+      <c r="E118" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -2875,16 +2864,16 @@
         <v>5</v>
       </c>
       <c r="B119">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E119">
-        <v>0.03</v>
+      <c r="D119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
@@ -2892,16 +2881,16 @@
         <v>5</v>
       </c>
       <c r="B120">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E120">
-        <v>0.03</v>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
@@ -2909,390 +2898,390 @@
         <v>5</v>
       </c>
       <c r="B121">
-        <v>2023</v>
+        <v>1961</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122">
+        <v>1961</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123">
+        <v>2023</v>
+      </c>
+      <c r="C123" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" t="s">
+        <v>77</v>
+      </c>
+      <c r="E123" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E124" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E125" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E126" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B128" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E121">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B122">
-        <v>2023</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122" s="1" t="s">
+      <c r="E128" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D129" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E122">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A123" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B123">
-        <v>2023</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D123" s="1" t="s">
+      <c r="E129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E123">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B124">
-        <v>2023</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D124" s="1" t="s">
+      <c r="E130" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E124">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B125">
-        <v>2023</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E125">
+      <c r="E131" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B126">
-        <v>2023</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E126">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B127">
-        <v>1961</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E127">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B128">
-        <v>2023</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E128">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B129">
-        <v>1961</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E129">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E132" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E133" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E134" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E135" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B130">
-        <v>2023</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E130">
+      <c r="E136" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B138" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E139" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" s="3">
+        <v>1961</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B131">
-        <v>2023</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B132">
-        <v>2023</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E132">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B133">
-        <v>2023</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E133">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B134">
-        <v>1961</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A135" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B135">
-        <v>2023</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A136" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B136">
-        <v>2023</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D136" t="s">
-        <v>14</v>
-      </c>
-      <c r="E136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B137">
-        <v>2023</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D137" t="s">
-        <v>15</v>
-      </c>
-      <c r="E137" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A138" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B138">
-        <v>2023</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D138" t="s">
-        <v>21</v>
-      </c>
-      <c r="E138" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B139">
-        <v>1961</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D139" t="s">
-        <v>14</v>
-      </c>
-      <c r="E139" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B140">
-        <v>1961</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="E140" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B141">
-        <v>1961</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D141" t="s">
-        <v>21</v>
-      </c>
-      <c r="E141" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>5</v>
-      </c>
-      <c r="B142">
-        <v>1961</v>
-      </c>
-      <c r="C142" t="s">
-        <v>25</v>
-      </c>
-      <c r="D142" t="s">
-        <v>80</v>
-      </c>
-      <c r="E142" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>5</v>
-      </c>
-      <c r="B143">
-        <v>2023</v>
-      </c>
-      <c r="C143" t="s">
-        <v>25</v>
-      </c>
-      <c r="D143" t="s">
-        <v>80</v>
-      </c>
-      <c r="E143" t="s">
-        <v>76</v>
+      <c r="E143">
+        <v>125</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
@@ -3303,13 +3292,13 @@
         <v>1961</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E144" s="8">
-        <v>2.76</v>
+        <v>9</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
@@ -3319,14 +3308,14 @@
       <c r="B145" s="3">
         <v>1961</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>32</v>
+      <c r="C145" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E145" s="8">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
@@ -3340,111 +3329,111 @@
         <v>33</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E146" s="8">
-        <v>2.5</v>
+        <v>21</v>
+      </c>
+      <c r="E146">
+        <v>150</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B147" s="3">
-        <v>1961</v>
+      <c r="A147" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" s="2">
+        <v>2023</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D147" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E147" s="8">
-        <v>2.2000000000000002</v>
+      <c r="D147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A148" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B148" s="2">
-        <v>1961</v>
+      <c r="A148" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" s="3">
+        <v>2023</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D148" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E148" s="8">
-        <v>2.2000000000000002</v>
+      <c r="D148" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B149" s="3">
-        <v>1961</v>
+      <c r="A149" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" s="2">
+        <v>2023</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D149" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E149" s="4">
+      <c r="D149" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E149">
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B150" s="2">
-        <v>1961</v>
+      <c r="A150" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150" s="3">
+        <v>2023</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" s="8">
-        <v>3.5</v>
+      <c r="D150" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150">
+        <v>125</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B151" s="3">
-        <v>1961</v>
+      <c r="A151" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151" s="2">
+        <v>2023</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D151" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" s="11">
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151">
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A152" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B152" s="2">
-        <v>1961</v>
+      <c r="A152" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152" s="3">
+        <v>2023</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E152" s="12">
+      <c r="D152" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152">
         <v>0</v>
       </c>
     </row>
@@ -3459,385 +3448,611 @@
         <v>33</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E153" s="8">
-        <v>2.5</v>
+        <v>21</v>
+      </c>
+      <c r="E153">
+        <v>150</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B154" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E154" s="8">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="A154" s="10"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="8"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B155" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E155" s="8">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="A155" s="9"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="8"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A156" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B156" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E156" s="4">
-        <v>0</v>
-      </c>
+      <c r="A156" s="10"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="4"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B157" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="8">
-        <v>3.5</v>
-      </c>
+      <c r="A157" s="9"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="8"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B158" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="11">
-        <v>0</v>
-      </c>
+      <c r="A158" s="10"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="11"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B159" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E159" s="12">
-        <v>0</v>
-      </c>
+      <c r="A159" s="9"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="12"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B160" s="2">
-        <v>1961</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A161" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B161" s="3">
-        <v>1961</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B162" s="2">
-        <v>1961</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B163" s="3">
-        <v>1961</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E163">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B164" s="2">
-        <v>1961</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B165" s="3">
-        <v>1961</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A166" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B166" s="2">
-        <v>1961</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E166">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A167" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B167" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A168" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B168" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B169" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A170" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B170" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D170" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E170">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A171" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B171" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A172" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B172" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A173" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B173" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E173">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A174" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B174" s="14">
-        <v>1961</v>
-      </c>
-      <c r="C174" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D174" t="s">
-        <v>39</v>
-      </c>
-      <c r="E174">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A175" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B175" s="14">
-        <v>2023</v>
-      </c>
-      <c r="C175" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D175" t="s">
-        <v>39</v>
-      </c>
-      <c r="E175">
-        <v>25</v>
-      </c>
+      <c r="A160" s="9"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" s="10"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="6"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" s="9"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163" s="10"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="6"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" s="9"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="10"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="6"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" s="9"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" s="9"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" s="10"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="6"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" s="9"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="10"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="6"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" s="9"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" s="10"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="6"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" s="9"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" s="13"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="15"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="13"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="15"/>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D244" s="16"/>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D245" s="17"/>
+    </row>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D246" s="16"/>
+    </row>
+    <row r="247" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D247" s="17"/>
+    </row>
+    <row r="248" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D248" s="16"/>
+    </row>
+    <row r="249" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D249" s="17"/>
+    </row>
+    <row r="250" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D250" s="17"/>
+    </row>
+    <row r="251" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D251" s="16"/>
+    </row>
+    <row r="252" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D252" s="17"/>
+    </row>
+    <row r="253" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D253" s="16"/>
+    </row>
+    <row r="254" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D254" s="17"/>
+    </row>
+    <row r="255" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D255" s="16"/>
+    </row>
+    <row r="256" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D256" s="17"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D257" s="17"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+      <c r="E260" s="1"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+      <c r="E261" s="1"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+      <c r="E262" s="1"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+      <c r="E265" s="1"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+      <c r="E266" s="1"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+      <c r="E267" s="1"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+      <c r="E268" s="1"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+      <c r="E269" s="1"/>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+      <c r="E294" s="1"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+      <c r="E295" s="1"/>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A296" s="1"/>
+      <c r="C296" s="1"/>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A297" s="1"/>
+      <c r="C297" s="1"/>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A298" s="1"/>
+      <c r="C298" s="1"/>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A299" s="1"/>
+      <c r="C299" s="1"/>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A300" s="1"/>
+      <c r="C300" s="1"/>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A301" s="1"/>
+      <c r="C301" s="1"/>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A304" s="9"/>
+      <c r="B304" s="2"/>
+      <c r="C304" s="5"/>
+      <c r="D304" s="5"/>
+      <c r="E304" s="8"/>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A305" s="10"/>
+      <c r="B305" s="3"/>
+      <c r="C305" s="6"/>
+      <c r="D305" s="6"/>
+      <c r="E305" s="8"/>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A306" s="9"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="5"/>
+      <c r="D306" s="5"/>
+      <c r="E306" s="8"/>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A307" s="10"/>
+      <c r="B307" s="3"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="6"/>
+      <c r="E307" s="8"/>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A308" s="9"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="5"/>
+      <c r="D308" s="5"/>
+      <c r="E308" s="8"/>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A309" s="10"/>
+      <c r="B309" s="3"/>
+      <c r="C309" s="5"/>
+      <c r="D309" s="6"/>
+      <c r="E309" s="4"/>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A310" s="9"/>
+      <c r="B310" s="2"/>
+      <c r="C310" s="5"/>
+      <c r="D310" s="5"/>
+      <c r="E310" s="8"/>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A311" s="10"/>
+      <c r="B311" s="3"/>
+      <c r="C311" s="5"/>
+      <c r="D311" s="6"/>
+      <c r="E311" s="11"/>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A312" s="9"/>
+      <c r="B312" s="2"/>
+      <c r="C312" s="5"/>
+      <c r="D312" s="5"/>
+      <c r="E312" s="12"/>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A313" s="9"/>
+      <c r="B313" s="2"/>
+      <c r="C313" s="5"/>
+      <c r="D313" s="5"/>
+      <c r="E313" s="8"/>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A314" s="10"/>
+      <c r="B314" s="3"/>
+      <c r="C314" s="5"/>
+      <c r="D314" s="6"/>
+      <c r="E314" s="8"/>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A315" s="9"/>
+      <c r="B315" s="2"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="5"/>
+      <c r="E315" s="8"/>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A316" s="10"/>
+      <c r="B316" s="3"/>
+      <c r="C316" s="5"/>
+      <c r="D316" s="6"/>
+      <c r="E316" s="4"/>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A317" s="9"/>
+      <c r="B317" s="2"/>
+      <c r="C317" s="5"/>
+      <c r="D317" s="5"/>
+      <c r="E317" s="8"/>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A318" s="10"/>
+      <c r="B318" s="3"/>
+      <c r="C318" s="5"/>
+      <c r="D318" s="6"/>
+      <c r="E318" s="11"/>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A319" s="9"/>
+      <c r="B319" s="2"/>
+      <c r="C319" s="5"/>
+      <c r="D319" s="5"/>
+      <c r="E319" s="12"/>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A320" s="9"/>
+      <c r="B320" s="2"/>
+      <c r="C320" s="5"/>
+      <c r="D320" s="5"/>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" s="10"/>
+      <c r="B321" s="3"/>
+      <c r="C321" s="5"/>
+      <c r="D321" s="6"/>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" s="9"/>
+      <c r="B322" s="2"/>
+      <c r="C322" s="5"/>
+      <c r="D322" s="5"/>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" s="10"/>
+      <c r="B323" s="3"/>
+      <c r="C323" s="5"/>
+      <c r="D323" s="6"/>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" s="9"/>
+      <c r="B324" s="2"/>
+      <c r="C324" s="5"/>
+      <c r="D324" s="5"/>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" s="10"/>
+      <c r="B325" s="3"/>
+      <c r="C325" s="5"/>
+      <c r="D325" s="6"/>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" s="9"/>
+      <c r="B326" s="2"/>
+      <c r="C326" s="5"/>
+      <c r="D326" s="5"/>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" s="9"/>
+      <c r="B327" s="2"/>
+      <c r="C327" s="5"/>
+      <c r="D327" s="5"/>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" s="10"/>
+      <c r="B328" s="3"/>
+      <c r="C328" s="5"/>
+      <c r="D328" s="6"/>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" s="9"/>
+      <c r="B329" s="2"/>
+      <c r="C329" s="5"/>
+      <c r="D329" s="5"/>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" s="10"/>
+      <c r="B330" s="3"/>
+      <c r="C330" s="5"/>
+      <c r="D330" s="6"/>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" s="9"/>
+      <c r="B331" s="2"/>
+      <c r="C331" s="5"/>
+      <c r="D331" s="5"/>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A332" s="10"/>
+      <c r="B332" s="3"/>
+      <c r="C332" s="5"/>
+      <c r="D332" s="6"/>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A333" s="9"/>
+      <c r="B333" s="2"/>
+      <c r="C333" s="5"/>
+      <c r="D333" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3859,315 +4074,315 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>0.65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>0.1</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0.25</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0.3</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0.1</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0.2</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0.4</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>0.6</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>0.1</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>0.05</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>0.1</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>0.05</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>0.1</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>0.5</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>0.3</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>0.2</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>0.3</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>0.1</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>0.2</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>0.4</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>0.3</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>0.05</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <v>0.05</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>0.05</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0.3</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>0.05</v>
@@ -4178,79 +4393,79 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>0.15</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B31">
         <v>0.2</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B32">
         <v>0.1</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33">
         <v>0.6</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B34">
         <v>0.1</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35">
         <v>0.5</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B36">
         <v>0.5</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4269,21 +4484,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
         <v>84</v>
-      </c>
-      <c r="B1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>0.78</v>
@@ -4291,10 +4506,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>0.5</v>
@@ -4302,10 +4517,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>0.23</v>
@@ -4313,10 +4528,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>0.25</v>
@@ -4324,10 +4539,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>0.1</v>
@@ -4335,10 +4550,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>0.1</v>
